--- a/data/trans_bre/P6902-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 15,16</t>
+          <t>-17,23; 16,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 35,11</t>
+          <t>1,08; 38,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 15,55</t>
+          <t>-21,48; 15,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 1,55</t>
+          <t>-19,44; 2,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 22,01</t>
+          <t>-20,15; 23,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 66,75</t>
+          <t>2,16; 79,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 24,09</t>
+          <t>-26,45; 24,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 1,73</t>
+          <t>-20,29; 2,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 34,86</t>
+          <t>-9,09; 35,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 17,58</t>
+          <t>-33,2; 18,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 38,6</t>
+          <t>-10,23; 39,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 12,39</t>
+          <t>-19,04; 10,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 83,21</t>
+          <t>-13,07; 85,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 29,87</t>
+          <t>-46,33; 30,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 92,55</t>
+          <t>-14,13; 87,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 16,53</t>
+          <t>-21,07; 13,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 8,41</t>
+          <t>-44,97; 4,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 30,22</t>
+          <t>-13,99; 28,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 63,4</t>
+          <t>-6,14; 59,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 28,79</t>
+          <t>-15,98; 28,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 19,67</t>
+          <t>-85,51; 10,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 93,03</t>
+          <t>-31,68; 84,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 239,64</t>
+          <t>-9,11; 221,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 76,11</t>
+          <t>-31,9; 78,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 33,08</t>
+          <t>1,55; 33,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 20,06</t>
+          <t>-9,44; 20,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 29,93</t>
+          <t>1,9; 29,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 24,3</t>
+          <t>-1,6; 23,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 118,56</t>
+          <t>4,28; 118,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 53,7</t>
+          <t>-18,73; 57,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 81,79</t>
+          <t>4,0; 81,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 51,64</t>
+          <t>-2,64; 51,85</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 19,1</t>
+          <t>-13,05; 19,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 44,96</t>
+          <t>1,26; 45,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 33,83</t>
+          <t>-1,66; 33,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 13,91</t>
+          <t>-37,19; 15,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 116,94</t>
+          <t>-39,37; 121,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 244,66</t>
+          <t>3,23; 268,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 192,8</t>
+          <t>-5,96; 178,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 34,26</t>
+          <t>-61,73; 40,6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,23%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,27; 15,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,11; 19,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,03; 26,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,58; 8,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,43; 39,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,33; 45,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,68; 65,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,57; 14,16</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,67</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-2,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 17,13</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 19,07</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8,18; 26,25</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-20,93; 7,96</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 43,04</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 44,65</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,1; 65,36</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-32,33; 13,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6902-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-11,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,36%</t>
+          <t>-12,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 16,1</t>
+          <t>-16,17; 16,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 38,44</t>
+          <t>0,56; 37,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 15,4</t>
+          <t>-21,8; 16,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 2,67</t>
+          <t>-20,54; -0,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 23,5</t>
+          <t>-20,19; 22,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 79,92</t>
+          <t>1,62; 74,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 24,11</t>
+          <t>-27,16; 25,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 2,96</t>
+          <t>-21,82; -1,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,82%</t>
+          <t>-3,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 35,78</t>
+          <t>-8,1; 34,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 18,2</t>
+          <t>-35,43; 18,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 39,72</t>
+          <t>-7,72; 40,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 10,39</t>
+          <t>-17,18; 13,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 85,72</t>
+          <t>-11,88; 84,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 30,87</t>
+          <t>-46,43; 30,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 87,71</t>
+          <t>-10,33; 88,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 13,58</t>
+          <t>-18,7; 16,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 4,77</t>
+          <t>-48,12; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 28,35</t>
+          <t>-14,38; 28,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 59,95</t>
+          <t>-2,95; 63,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 28,92</t>
+          <t>-17,28; 27,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-85,51; 10,58</t>
+          <t>-86,77; 15,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 84,53</t>
+          <t>-31,34; 84,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 221,07</t>
+          <t>-9,39; 229,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 78,39</t>
+          <t>-29,75; 68,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 33,83</t>
+          <t>3,95; 34,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 20,34</t>
+          <t>-9,17; 21,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 29,76</t>
+          <t>2,02; 29,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 23,74</t>
+          <t>-1,65; 21,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 118,84</t>
+          <t>11,37; 121,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 57,25</t>
+          <t>-19,88; 60,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 81,55</t>
+          <t>3,87; 81,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 51,85</t>
+          <t>-2,41; 45,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>12,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-14,44%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 19,34</t>
+          <t>-13,54; 19,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 45,81</t>
+          <t>0,52; 45,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 33,33</t>
+          <t>-0,85; 33,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 15,93</t>
+          <t>-2,83; 30,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 121,1</t>
+          <t>-41,3; 121,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 268,63</t>
+          <t>-1,53; 279,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 178,98</t>
+          <t>-6,28; 192,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 40,6</t>
+          <t>-4,58; 97,21</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-2,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,65</t>
+          <t>-0,25; 15,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,13</t>
+          <t>1,2; 18,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,03; 26,24</t>
+          <t>8,58; 25,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 8,33</t>
+          <t>-1,39; 12,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 39,4</t>
+          <t>-0,4; 39,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 45,6</t>
+          <t>2,74; 44,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 65,5</t>
+          <t>18,79; 64,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 14,16</t>
+          <t>-2,07; 20,89</t>
         </is>
       </c>
     </row>
